--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__combo_fit_RV__HSA_Score_RV.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__combo_fit_RV__HSA_Score_RV.xlsx
@@ -376,560 +376,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.1884023545641392</v>
+        <v>0.2150052498427152</v>
       </c>
       <c r="C2">
-        <v>0.1572816875641388</v>
+        <v>0.3093066493645196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.147851573930432</v>
+        <v>0.2336834221524121</v>
       </c>
       <c r="C3">
-        <v>0.1419651702738729</v>
+        <v>0.2128946764385344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.1473611793057641</v>
+        <v>0.2685650194586292</v>
       </c>
       <c r="C4">
-        <v>0.1624029444825528</v>
+        <v>0.203270790285546</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.1852519772620458</v>
+        <v>0.03770017134068475</v>
       </c>
       <c r="C5">
-        <v>0.2312508629551594</v>
+        <v>0.283983223303281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.2685650194586292</v>
+        <v>0.1112186474471384</v>
       </c>
       <c r="C6">
-        <v>0.203270790285546</v>
+        <v>0.146340851675394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.2336834221524121</v>
+        <v>0.2074602728949222</v>
       </c>
       <c r="C7">
-        <v>0.2128946764385344</v>
+        <v>0.5119367321970379</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.1426292421198837</v>
+        <v>0.1506787392396111</v>
       </c>
       <c r="C8">
-        <v>0.4723799116905842</v>
+        <v>0.2087728370367761</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.1800833554275388</v>
+        <v>0.1977494448019222</v>
       </c>
       <c r="C9">
-        <v>0.3387093581742073</v>
+        <v>0.4039812855817344</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.1483605966345773</v>
+        <v>0.2462551586804521</v>
       </c>
       <c r="C10">
-        <v>0.1973583426879742</v>
+        <v>0.1724140092707299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.2074602728949222</v>
+        <v>0.1884023545641392</v>
       </c>
       <c r="C11">
-        <v>0.5119367321970379</v>
+        <v>0.1572816875641388</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.1112186474471384</v>
+        <v>0.2886380853908625</v>
       </c>
       <c r="C12">
-        <v>0.146340851675394</v>
+        <v>0.1921884969214541</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.2150052498427152</v>
+        <v>0.187133466248112</v>
       </c>
       <c r="C13">
-        <v>0.3093066493645196</v>
+        <v>0.1915886716207848</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.04570006327085658</v>
+        <v>0.1310694780430076</v>
       </c>
       <c r="C14">
-        <v>0.2568488129343509</v>
+        <v>0.153296899975375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.06543841004005117</v>
+        <v>0.1547748683161573</v>
       </c>
       <c r="C15">
-        <v>0.3131780868089317</v>
+        <v>0.1493100503047665</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.121164783724253</v>
+        <v>0.1800833554275388</v>
       </c>
       <c r="C16">
-        <v>0.1993396770985001</v>
+        <v>0.3387093581742073</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.09064879953010098</v>
+        <v>0.1430966213669971</v>
       </c>
       <c r="C17">
-        <v>0.5287174908829064</v>
+        <v>0.1115718628279053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.2462551586804521</v>
+        <v>0.1327717250558471</v>
       </c>
       <c r="C18">
-        <v>0.1724140092707299</v>
+        <v>0.1137361100309824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.1735849848804177</v>
+        <v>0.1012706344452991</v>
       </c>
       <c r="C19">
-        <v>0.1915067048345555</v>
+        <v>0.3047006025897885</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.1941286399551475</v>
+        <v>0.09518337451122398</v>
       </c>
       <c r="C20">
-        <v>0.1357032561361763</v>
+        <v>0.4110678898993151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.1320909498930296</v>
+        <v>0.2253887245915078</v>
       </c>
       <c r="C21">
-        <v>0.1217990631839138</v>
+        <v>0.2117390573524804</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.2886380853908625</v>
+        <v>0.1483605966345773</v>
       </c>
       <c r="C22">
-        <v>0.1921884969214541</v>
+        <v>0.1973583426879742</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.1506787392396111</v>
+        <v>0.1473611793057641</v>
       </c>
       <c r="C23">
-        <v>0.2087728370367761</v>
+        <v>0.1624029444825528</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.3162200191222009</v>
+        <v>0.09064879953010098</v>
       </c>
       <c r="C24">
-        <v>0.1000904857800615</v>
+        <v>0.5287174908829064</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.09922053660239878</v>
+        <v>0.1971210295949406</v>
       </c>
       <c r="C25">
-        <v>0.09196702944835715</v>
+        <v>0.2701509675529902</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.2244797744913844</v>
+        <v>0.09597800461743138</v>
       </c>
       <c r="C26">
-        <v>0.1798229650070454</v>
+        <v>0.248765209527911</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.2314277205455031</v>
+        <v>0.1852519772620458</v>
       </c>
       <c r="C27">
-        <v>0.17267192649217</v>
+        <v>0.2312508629551594</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.1971210295949406</v>
+        <v>0.2244797744913844</v>
       </c>
       <c r="C28">
-        <v>0.2701509675529902</v>
+        <v>0.1798229650070454</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.09597800461743138</v>
+        <v>0.06543841004005117</v>
       </c>
       <c r="C29">
-        <v>0.248765209527911</v>
+        <v>0.3131780868089317</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.187133466248112</v>
+        <v>0.1554645638993872</v>
       </c>
       <c r="C30">
-        <v>0.1915886716207848</v>
+        <v>0.1095207215113446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.1310694780430076</v>
+        <v>0.1426292421198837</v>
       </c>
       <c r="C31">
-        <v>0.153296899975375</v>
+        <v>0.4723799116905842</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.1327717250558471</v>
+        <v>0.09834336499802618</v>
       </c>
       <c r="C32">
-        <v>0.1137361100309824</v>
+        <v>0.1685483270061995</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.1554645638993872</v>
+        <v>0.1735849848804177</v>
       </c>
       <c r="C33">
-        <v>0.1095207215113446</v>
+        <v>0.1915067048345555</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.1616835248699598</v>
+        <v>0.04570006327085658</v>
       </c>
       <c r="C34">
-        <v>0.1356822282680572</v>
+        <v>0.2568488129343509</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.09834336499802618</v>
+        <v>0.1320909498930296</v>
       </c>
       <c r="C35">
-        <v>0.1685483270061995</v>
+        <v>0.1217990631839138</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.1547748683161573</v>
+        <v>0.147851573930432</v>
       </c>
       <c r="C36">
-        <v>0.1493100503047665</v>
+        <v>0.1419651702738729</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.09518337451122398</v>
+        <v>0.1616835248699598</v>
       </c>
       <c r="C37">
-        <v>0.4110678898993151</v>
+        <v>0.1356822282680572</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.1012706344452991</v>
+        <v>0.121164783724253</v>
       </c>
       <c r="C38">
-        <v>0.3047006025897885</v>
+        <v>0.1993396770985001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.2004329726360979</v>
+        <v>0.1904734599287308</v>
       </c>
       <c r="C39">
-        <v>0.1443868357419467</v>
+        <v>0.2076953706434155</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.1904734599287308</v>
+        <v>0.3162200191222009</v>
       </c>
       <c r="C40">
-        <v>0.2076953706434155</v>
+        <v>0.1000904857800615</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.1430966213669971</v>
+        <v>0.2004329726360979</v>
       </c>
       <c r="C41">
-        <v>0.1115718628279053</v>
+        <v>0.1443868357419467</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.03770017134068475</v>
+        <v>0.1941286399551475</v>
       </c>
       <c r="C42">
-        <v>0.283983223303281</v>
+        <v>0.1357032561361763</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.2253887245915078</v>
+        <v>0.09922053660239878</v>
       </c>
       <c r="C43">
-        <v>0.2117390573524804</v>
+        <v>0.09196702944835715</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.1977494448019222</v>
+        <v>0.2314277205455031</v>
       </c>
       <c r="C44">
-        <v>0.4039812855817344</v>
+        <v>0.17267192649217</v>
       </c>
     </row>
   </sheetData>
@@ -957,7 +957,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1173,7 +1173,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1197,7 +1197,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1305,7 +1305,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1365,7 +1365,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1437,7 +1437,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
